--- a/AAII_Financials/Yearly/WATT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/WATT_YR_FIN.xlsx
@@ -1009,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="E14" s="3">
         <v>1600</v>
@@ -1252,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-300</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>-200</v>
@@ -1303,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-8600</v>
+        <v>-9200</v>
       </c>
       <c r="E21" s="3">
         <v>-16600</v>
@@ -1864,7 +1864,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>300</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>200</v>
